--- a/data/proteomics/GEM_volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
+++ b/data/proteomics/GEM_volume_size_across_compartment_Rosemary_NH4_limitation_v2.xlsx
@@ -535,58 +535,58 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3894490502743549</v>
+        <v>0.3897130771675298</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3510343625665092</v>
+        <v>0.3512692421762204</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3593867758142417</v>
+        <v>0.3596641757544101</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2965902489609162</v>
+        <v>0.2968073518155828</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3086520804545104</v>
+        <v>0.3088866523207013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.434401018531885</v>
+        <v>0.4347498249696976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4504980002229833</v>
+        <v>0.4508879341536476</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3895038152326306</v>
+        <v>0.3898191952940782</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3944104686549829</v>
+        <v>0.3947351531114516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.42530587594738</v>
+        <v>0.4256214512087037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4252825253759856</v>
+        <v>0.4256236753087322</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4381164308460764</v>
+        <v>0.4384519808598666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.756971375872142</v>
+        <v>0.7574727553648551</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7666527490401289</v>
+        <v>0.767143893356204</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7116298780330298</v>
+        <v>0.712185016513998</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9299458968878855</v>
+        <v>0.9305864866469952</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9874877727827561</v>
+        <v>0.9882344847020327</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9873379945219077</v>
+        <v>0.9879485223116248</v>
       </c>
     </row>
     <row r="3">
@@ -666,55 +666,55 @@
         <v>9.145507467136577e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>8.399706263633145e-05</v>
+        <v>0.0001166964066860348</v>
       </c>
       <c r="E4" t="n">
-        <v>8.874438097010205e-05</v>
+        <v>0.0001406400189907373</v>
       </c>
       <c r="F4" t="n">
-        <v>9.552645052735991e-05</v>
+        <v>0.0001608145080193977</v>
       </c>
       <c r="G4" t="n">
-        <v>9.587727515252078e-05</v>
+        <v>0.0001605308512717759</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001644186660830054</v>
+        <v>0.0001644186660830055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001618083879397892</v>
+        <v>0.00024616471333617</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000136065543617162</v>
+        <v>0.0002161983717191757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001374605825678186</v>
+        <v>0.0001765710836165824</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001558958686867174</v>
+        <v>0.0001558958686867175</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001524623867037577</v>
+        <v>0.0002609149383655306</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001618846306687894</v>
+        <v>0.0002818833878427303</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002438827686301801</v>
+        <v>0.0003462511656911554</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000217807428437864</v>
+        <v>0.0003749962757647411</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002241462457437782</v>
+        <v>0.000356193932193973</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002525138696124552</v>
+        <v>0.000390146212228284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002677123078621684</v>
+        <v>0.0003646921725465284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002923556225563443</v>
+        <v>0.0004815074088812674</v>
       </c>
     </row>
     <row r="5">
@@ -727,58 +727,58 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.007976138553387703</v>
+        <v>0.008245839527922818</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007313790945165651</v>
+        <v>0.007553613437203938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007563735699817293</v>
+        <v>0.007844696238842866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00804511254150132</v>
+        <v>0.008266525369502828</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008214166514106917</v>
+        <v>0.008453339515005372</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01145711896140908</v>
+        <v>0.01179146441102673</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01432741199457606</v>
+        <v>0.01471536696662813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0122277356742847</v>
+        <v>0.01254155466855583</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01248587190362038</v>
+        <v>0.01280803314184606</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01523428332967738</v>
+        <v>0.01555679054190954</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01522813766541178</v>
+        <v>0.01556946237569489</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01453670403154178</v>
+        <v>0.01487544158591108</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02677810773308539</v>
+        <v>0.02727760963456996</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02836493556264047</v>
+        <v>0.02885538060822509</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0244780956781472</v>
+        <v>0.0250344980975849</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03043399690302368</v>
+        <v>0.03107751731707488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03147449328139611</v>
+        <v>0.03220892147452456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03173858229195327</v>
+        <v>0.03234931113990112</v>
       </c>
     </row>
     <row r="6">
@@ -791,58 +791,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1399941059794014</v>
+        <v>0.1399949285621868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1240196892806926</v>
+        <v>0.1240204001706863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1315996316101052</v>
+        <v>0.1316002063558558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1162772482678268</v>
+        <v>0.1162778424358843</v>
       </c>
       <c r="G6" t="n">
         <v>0.1195216121703475</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1502354228033976</v>
+        <v>0.1502362541546042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1729926795416006</v>
+        <v>0.1729940520323431</v>
       </c>
       <c r="J6" t="n">
         <v>0.1543522999976052</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1497674445800449</v>
+        <v>0.1497686514168601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1564385206484832</v>
+        <v>0.156440086548717</v>
       </c>
       <c r="M6" t="n">
-        <v>0.161434754103247</v>
+        <v>0.1614363854053451</v>
       </c>
       <c r="N6" t="n">
         <v>0.1659319396601063</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2864577537282781</v>
+        <v>0.2864620291613879</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2873268660206058</v>
+        <v>0.2873323196815913</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2785069734978273</v>
+        <v>0.2785111290107337</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3768672317574859</v>
+        <v>0.3768736892867774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4149182377734678</v>
+        <v>0.4149238003981155</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3778902531596509</v>
+        <v>0.3778902531596506</v>
       </c>
     </row>
     <row r="7">
@@ -855,58 +855,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3380025033360834</v>
+        <v>0.3382218159815653</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3037735282930704</v>
+        <v>0.3037782177950843</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3127907961859195</v>
+        <v>0.3130074606377855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2695488264287659</v>
+        <v>0.2695541073914324</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2843696345990002</v>
+        <v>0.2845935840563291</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3849151389402407</v>
+        <v>0.3850947427131312</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4028892791461405</v>
+        <v>0.4028986883235997</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3420310921593968</v>
+        <v>0.3422748784293806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3505618227992754</v>
+        <v>0.3505694247318978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4065799737888974</v>
+        <v>0.4067973378039564</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3954559251608574</v>
+        <v>0.3956543834855744</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3992846527607085</v>
+        <v>0.3995665265375369</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7466853396317733</v>
+        <v>0.7467039293625382</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548919169211694</v>
+        <v>0.7551138240707739</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7361104597516281</v>
+        <v>0.736129893273801</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9681017201401991</v>
+        <v>0.9683849362319644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9949206383101979</v>
+        <v>0.9949479034456676</v>
       </c>
       <c r="T7" t="n">
-        <v>1.011580883037759</v>
+        <v>1.012011034900297</v>
       </c>
     </row>
     <row r="8">
@@ -919,58 +919,58 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.205920218370407</v>
+        <v>0.2061350265814562</v>
       </c>
       <c r="D8" t="n">
         <v>0.1759685672484304</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1786988956923776</v>
+        <v>0.1789148638035318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1583957137794151</v>
+        <v>0.1583976449432737</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1606756718697064</v>
+        <v>0.1608978852554118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2578832707746397</v>
+        <v>0.2580566694552667</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2529078603785377</v>
+        <v>0.2529104893843601</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2195757305687883</v>
+        <v>0.2198148740426422</v>
       </c>
       <c r="K8" t="n">
         <v>0.2133431429126259</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2147301063919325</v>
+        <v>0.2149413928875134</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2233865118506316</v>
+        <v>0.2235836119120387</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2253782873192387</v>
+        <v>0.2256562488772772</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4216752515280069</v>
+        <v>0.4216752515280068</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4236429635885244</v>
+        <v>0.423860117486303</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4087754912991672</v>
+        <v>0.4087793972592356</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5742683389219372</v>
+        <v>0.5745450738032297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6423519506930794</v>
+        <v>0.6423558624425451</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5987853903046081</v>
+        <v>0.5991981286987531</v>
       </c>
     </row>
     <row r="9">
@@ -1090,7 +1090,7 @@
         <v>0.02916720264980864</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08211366793693972</v>
+        <v>0.08211366793693974</v>
       </c>
       <c r="I11" t="n">
         <v>0.06355346301350763</v>
@@ -1139,58 +1139,58 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01501367162031547</v>
+        <v>0.01528164693997583</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01340654634117867</v>
+        <v>0.01364636883321696</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01403852256273375</v>
+        <v>0.01431727677827832</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01283411054805928</v>
+        <v>0.01305359221220212</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01453923650344672</v>
+        <v>0.01477654173169284</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01515298574965707</v>
+        <v>0.01548589490245075</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02328432100699461</v>
+        <v>0.02366964697322454</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01988435544191307</v>
+        <v>0.02019608307115522</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02021643346529965</v>
+        <v>0.02053859470352533</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02424071749903541</v>
+        <v>0.02456009286670907</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02219068124283862</v>
+        <v>0.02252945425524163</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02410385919248159</v>
+        <v>0.02443953848116981</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03468863295821863</v>
+        <v>0.03518813485970323</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03556554388497254</v>
+        <v>0.03605188856862292</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.03512961377973511</v>
+        <v>0.03568211023910434</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03875847728814996</v>
+        <v>0.03939788938422697</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04006158666990232</v>
+        <v>0.04079210311356484</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04229297023807334</v>
+        <v>0.04289925642726265</v>
       </c>
     </row>
     <row r="13">
@@ -1267,58 +1267,58 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.006656814270920206</v>
+        <v>0.006924789590580566</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006125207369923348</v>
+        <v>0.006365029861961635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006237440075041106</v>
+        <v>0.006516194290585672</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004663676182403998</v>
+        <v>0.004883157846546834</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005245383798803771</v>
+        <v>0.005482689027049897</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006633700627627869</v>
+        <v>0.006966609780421547</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008311046581137847</v>
+        <v>0.00869637254736778</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006843813597307834</v>
+        <v>0.007155541226549974</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007166858645708749</v>
+        <v>0.00748901988393443</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008430893931727657</v>
+        <v>0.00875026929940133</v>
       </c>
       <c r="M14" t="n">
-        <v>0.008335358697174035</v>
+        <v>0.008674131709577057</v>
       </c>
       <c r="N14" t="n">
-        <v>0.008387827419416379</v>
+        <v>0.008723506708104588</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01280300355810984</v>
+        <v>0.01330250545959442</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01307805238032655</v>
+        <v>0.01356439706397694</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01121242554521244</v>
+        <v>0.01176492200458167</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01358988372478002</v>
+        <v>0.014229295820857</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01278384306878288</v>
+        <v>0.0135143595124454</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01487430096174952</v>
+        <v>0.01548058715093883</v>
       </c>
     </row>
     <row r="15">
@@ -1349,7 +1349,7 @@
         <v>0.0009633036672693288</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001160357294757739</v>
+        <v>0.001160357294757738</v>
       </c>
       <c r="J15" t="n">
         <v>0.0009682257673118017</v>
@@ -1398,55 +1398,55 @@
         <v>0.002724844536099343</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002394491248811147</v>
+        <v>0.00242719059286085</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002402757300146892</v>
+        <v>0.002454652938167527</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002673801399853969</v>
+        <v>0.002739089457346006</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00276195196651592</v>
+        <v>0.002826605542635175</v>
       </c>
       <c r="H16" t="n">
         <v>0.002748045624263448</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004469930797410938</v>
+        <v>0.004554287122807317</v>
       </c>
       <c r="J16" t="n">
-        <v>0.003893194086544094</v>
+        <v>0.003973326914646108</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003888273980158429</v>
+        <v>0.003927384481207192</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005009873436579914</v>
+        <v>0.005009873436579916</v>
       </c>
       <c r="M16" t="n">
-        <v>0.004917082793271223</v>
+        <v>0.005025535344932996</v>
       </c>
       <c r="N16" t="n">
-        <v>0.005075316906963522</v>
+        <v>0.005195315664137462</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008430421370183513</v>
+        <v>0.008532789767244487</v>
       </c>
       <c r="P16" t="n">
-        <v>0.008098054261999056</v>
+        <v>0.008255243109325934</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.007978161060111136</v>
+        <v>0.008110208746561331</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01053516823636063</v>
+        <v>0.01067280057897646</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01078066752918456</v>
+        <v>0.01087764739386892</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01057087780260753</v>
+        <v>0.01076002958893246</v>
       </c>
     </row>
     <row r="17">
@@ -1459,58 +1459,58 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.004249472735812441</v>
+        <v>0.004251198390687195</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003662303097072541</v>
+        <v>0.00366230309707254</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003783421351245497</v>
+        <v>0.003785627674726503</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003824549064842014</v>
+        <v>0.003826480228700684</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004592637079688345</v>
+        <v>0.004594504852340676</v>
       </c>
       <c r="H17" t="n">
-        <v>0.003376827131871445</v>
+        <v>0.003378263428695418</v>
       </c>
       <c r="I17" t="n">
-        <v>0.006988309240204009</v>
+        <v>0.006990938246026141</v>
       </c>
       <c r="J17" t="n">
-        <v>0.005574478124230417</v>
+        <v>0.005576569489259407</v>
       </c>
       <c r="K17" t="n">
         <v>0.006232251635692444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007020130788055651</v>
+        <v>0.007023262632614147</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005927895235768748</v>
+        <v>0.005930446933648846</v>
       </c>
       <c r="N17" t="n">
-        <v>0.007178652170730435</v>
+        <v>0.007181710436411528</v>
       </c>
       <c r="O17" t="n">
         <v>0.008402136061500389</v>
       </c>
       <c r="P17" t="n">
-        <v>0.007889149093227939</v>
+        <v>0.00789324945516217</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.00787614785158056</v>
+        <v>0.007880053811649034</v>
       </c>
       <c r="R17" t="n">
-        <v>0.006984543874946722</v>
+        <v>0.00698865219292094</v>
       </c>
       <c r="S17" t="n">
-        <v>0.006615484043659896</v>
+        <v>0.006619395793125833</v>
       </c>
       <c r="T17" t="n">
-        <v>0.008436085152823562</v>
+        <v>0.008440527811582105</v>
       </c>
     </row>
     <row r="18">
@@ -1523,58 +1523,58 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0005796191871277565</v>
+        <v>0.0008475945067881171</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004957930888389666</v>
+        <v>0.0007356155808772536</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0005522568277932863</v>
+        <v>0.0008310110433378532</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0006364663481202351</v>
+        <v>0.0008559480122630726</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0006563561498363558</v>
+        <v>0.00089366137808248</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0005541288430347123</v>
+        <v>0.0008870379958283908</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001011455278714048</v>
+        <v>0.001396781244943983</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0009426779289084712</v>
+        <v>0.001254405558150611</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000931513195606384</v>
+        <v>0.001253674433832066</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001249336769225648</v>
+        <v>0.001568712136899319</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001177741385827407</v>
+        <v>0.00151651439823043</v>
       </c>
       <c r="N18" t="n">
-        <v>0.001254977860610885</v>
+        <v>0.001590657149299097</v>
       </c>
       <c r="O18" t="n">
-        <v>0.00187831222754112</v>
+        <v>0.002377814129025689</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001898821363794291</v>
+        <v>0.002385166047444682</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.002243078726218045</v>
+        <v>0.002795575185587272</v>
       </c>
       <c r="R18" t="n">
-        <v>0.002552140029758594</v>
+        <v>0.003191552125835581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0028154676713482</v>
+        <v>0.003545984115010713</v>
       </c>
       <c r="T18" t="n">
-        <v>0.002781044341911777</v>
+        <v>0.003387330531101087</v>
       </c>
     </row>
     <row r="19">
@@ -1587,58 +1587,58 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001316741603117362</v>
+        <v>0.001584716922777723</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001120289964985909</v>
+        <v>0.001360112457024196</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001228705447110389</v>
+        <v>0.001507459662654955</v>
       </c>
       <c r="F19" t="n">
-        <v>0.001427330853381452</v>
+        <v>0.00164681251752429</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001449562773819255</v>
+        <v>0.001686868002065379</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001219395687356225</v>
+        <v>0.001552304840149904</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002128796729773462</v>
+        <v>0.002514122696003397</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00195731403598892</v>
+        <v>0.00226904166523106</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001943029352547205</v>
+        <v>0.002265190590772888</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002488316761983436</v>
+        <v>0.002807692129657106</v>
       </c>
       <c r="M19" t="n">
-        <v>0.002364578216594942</v>
+        <v>0.002703351228997964</v>
       </c>
       <c r="N19" t="n">
-        <v>0.002531426623764667</v>
+        <v>0.002867105912452879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003539294203323791</v>
+        <v>0.004038796104808361</v>
       </c>
       <c r="P19" t="n">
-        <v>0.003534891611410668</v>
+        <v>0.004021236295061059</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003990299617266804</v>
+        <v>0.004542796076636031</v>
       </c>
       <c r="R19" t="n">
-        <v>0.004623181049861836</v>
+        <v>0.005262593145938821</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004793506630546655</v>
+        <v>0.005524023074209169</v>
       </c>
       <c r="T19" t="n">
-        <v>0.004949153566523598</v>
+        <v>0.005555439755712909</v>
       </c>
     </row>
     <row r="20">
@@ -1651,58 +1651,58 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007215422798364271</v>
+        <v>0.007483398118024632</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006165068644892176</v>
+        <v>0.006404891136930464</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007224063708240785</v>
+        <v>0.007502817923785351</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00687003360885742</v>
+        <v>0.007089515273000258</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007452447916633859</v>
+        <v>0.007689753144879984</v>
       </c>
       <c r="H20" t="n">
-        <v>0.009415166123934548</v>
+        <v>0.009748075276728226</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01038810359434396</v>
+        <v>0.01077342956057389</v>
       </c>
       <c r="J20" t="n">
-        <v>0.008901171366389841</v>
+        <v>0.009212898995631982</v>
       </c>
       <c r="K20" t="n">
-        <v>0.009278915442145031</v>
+        <v>0.009601076680370713</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0125268179526013</v>
+        <v>0.01284619332027498</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01296803201748263</v>
+        <v>0.01330680502988565</v>
       </c>
       <c r="N20" t="n">
-        <v>0.01059549679258995</v>
+        <v>0.01093117608127816</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02749442622009167</v>
+        <v>0.02799392812157624</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02685647085124174</v>
+        <v>0.02734281553489213</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02646362981190961</v>
+        <v>0.02701612627127884</v>
       </c>
       <c r="R20" t="n">
-        <v>0.03361998006211137</v>
+        <v>0.03425939215818836</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02898263050121115</v>
+        <v>0.02971314694487367</v>
       </c>
       <c r="T20" t="n">
-        <v>0.03570395417343681</v>
+        <v>0.03631024036262612</v>
       </c>
     </row>
     <row r="21">
@@ -1810,10 +1810,10 @@
         <v>0.06042811707357148</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04849610681135955</v>
+        <v>0.04849610681135956</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0424497221162301</v>
+        <v>0.04244972211623009</v>
       </c>
       <c r="F23" t="n">
         <v>0.03833999259535201</v>
@@ -1822,7 +1822,7 @@
         <v>0.03671356110234754</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09296687667671537</v>
+        <v>0.09296687667671541</v>
       </c>
       <c r="I23" t="n">
         <v>0.07584958194234369</v>
@@ -1834,7 +1834,7 @@
         <v>0.0604239824718966</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05661803948459566</v>
+        <v>0.05661803948459564</v>
       </c>
       <c r="M23" t="n">
         <v>0.06265267413394981</v>
@@ -1858,7 +1858,7 @@
         <v>0.214598574078276</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1786214175998391</v>
+        <v>0.178621417599839</v>
       </c>
     </row>
     <row r="24">
@@ -1963,58 +1963,58 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0005796191871277565</v>
+        <v>0.0008475945067881171</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0004957930888389666</v>
+        <v>0.0007356155808772536</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0005522568277932863</v>
+        <v>0.0008310110433378532</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0006364663481202351</v>
+        <v>0.0008559480122630726</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0006563561498363558</v>
+        <v>0.00089366137808248</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0005541288430347123</v>
+        <v>0.0008870379958283908</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001011455278714048</v>
+        <v>0.001396781244943983</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0009426779289084712</v>
+        <v>0.001254405558150611</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000931513195606384</v>
+        <v>0.001253674433832066</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001249336769225648</v>
+        <v>0.001568712136899319</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001177741385827407</v>
+        <v>0.00151651439823043</v>
       </c>
       <c r="N26" t="n">
-        <v>0.001254977860610885</v>
+        <v>0.001590657149299097</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00187831222754112</v>
+        <v>0.002377814129025689</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001898821363794291</v>
+        <v>0.002385166047444682</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.002243078726218045</v>
+        <v>0.002795575185587272</v>
       </c>
       <c r="R26" t="n">
-        <v>0.002552140029758594</v>
+        <v>0.003191552125835581</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0028154676713482</v>
+        <v>0.003545984115010713</v>
       </c>
       <c r="T26" t="n">
-        <v>0.002781044341911777</v>
+        <v>0.003387330531101087</v>
       </c>
     </row>
     <row r="27">
@@ -2109,22 +2109,22 @@
         <v>4.637498537492535e-05</v>
       </c>
       <c r="I28" t="n">
-        <v>6.564696439773134e-05</v>
+        <v>6.564696439773133e-05</v>
       </c>
       <c r="J28" t="n">
-        <v>5.923390693674823e-05</v>
+        <v>5.923390693674822e-05</v>
       </c>
       <c r="K28" t="n">
         <v>5.924928413918553e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>6.946552613778796e-05</v>
+        <v>6.946552613778795e-05</v>
       </c>
       <c r="M28" t="n">
         <v>6.676747844744138e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>7.152971513301979e-05</v>
+        <v>7.15297151330198e-05</v>
       </c>
       <c r="O28" t="n">
         <v>0.0001092025760946123</v>
@@ -2155,58 +2155,58 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0178879916025102</v>
+        <v>0.01815769257704532</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01696632034625392</v>
+        <v>0.01720614283829221</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01667414415582847</v>
+        <v>0.01695510469485404</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01705630580556162</v>
+        <v>0.01727771863356312</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01988557012725073</v>
+        <v>0.02012474312814919</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01466640405889446</v>
+        <v>0.01500074950851211</v>
       </c>
       <c r="I29" t="n">
-        <v>0.020596992022437</v>
+        <v>0.02098494699448906</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01813043512717055</v>
+        <v>0.01844425412144168</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02075352940280081</v>
+        <v>0.0210756906410265</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02380711038299585</v>
+        <v>0.02412961759522802</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02246789992779854</v>
+        <v>0.02280922463808168</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02356714074345447</v>
+        <v>0.02390587829782378</v>
       </c>
       <c r="O29" t="n">
-        <v>0.03705777528364183</v>
+        <v>0.03755727718512641</v>
       </c>
       <c r="P29" t="n">
-        <v>0.03807877620090547</v>
+        <v>0.03856922124649009</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.03793440760298075</v>
+        <v>0.03849081002241845</v>
       </c>
       <c r="R29" t="n">
-        <v>0.04392729481581582</v>
+        <v>0.04457081522986702</v>
       </c>
       <c r="S29" t="n">
-        <v>0.03819582281452576</v>
+        <v>0.03893025100765421</v>
       </c>
       <c r="T29" t="n">
-        <v>0.04643280647976504</v>
+        <v>0.04704353532771291</v>
       </c>
     </row>
     <row r="30">
@@ -2284,7 +2284,7 @@
         <v>0.02161779998343698</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01974993000049867</v>
+        <v>0.01974993000049868</v>
       </c>
       <c r="G32" t="n">
         <v>0.02193113393749718</v>
@@ -2293,40 +2293,40 @@
         <v>0.02591030089324741</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02843900569241114</v>
+        <v>0.02843900569241113</v>
       </c>
       <c r="J32" t="n">
         <v>0.02454238880964213</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02470614105031515</v>
+        <v>0.02470614105031516</v>
       </c>
       <c r="L32" t="n">
         <v>0.02961102300403871</v>
       </c>
       <c r="M32" t="n">
-        <v>0.03044985652162666</v>
+        <v>0.03044985652162667</v>
       </c>
       <c r="N32" t="n">
         <v>0.03039771148116659</v>
       </c>
       <c r="O32" t="n">
-        <v>0.05861442342843672</v>
+        <v>0.05861442342843673</v>
       </c>
       <c r="P32" t="n">
         <v>0.05919572969245029</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.05602697729433655</v>
+        <v>0.05602697729433657</v>
       </c>
       <c r="R32" t="n">
         <v>0.07429087736429418</v>
       </c>
       <c r="S32" t="n">
-        <v>0.08478847349065646</v>
+        <v>0.0847884734906565</v>
       </c>
       <c r="T32" t="n">
-        <v>0.07634580215768651</v>
+        <v>0.07634580215768652</v>
       </c>
     </row>
     <row r="33">
@@ -2354,7 +2354,7 @@
         <v>0.03111362090904359</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03310131540082506</v>
+        <v>0.03310131540082507</v>
       </c>
       <c r="I33" t="n">
         <v>0.04034472116921295</v>
@@ -2375,7 +2375,7 @@
         <v>0.04153914693994923</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06488713913625342</v>
+        <v>0.06488713913625344</v>
       </c>
       <c r="P33" t="n">
         <v>0.06715079581628465</v>
@@ -2387,10 +2387,10 @@
         <v>0.07167227067311786</v>
       </c>
       <c r="S33" t="n">
-        <v>0.06923941991853257</v>
+        <v>0.06923941991853255</v>
       </c>
       <c r="T33" t="n">
-        <v>0.07093696377453795</v>
+        <v>0.07093696377453794</v>
       </c>
     </row>
     <row r="34">
@@ -2402,24 +2402,60 @@
           <t>incipient cellular bud site</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>0.0002679753196603606</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.000239822492038287</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0002787542155445669</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0002194816641428375</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0002373052282461242</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0003329091527936784</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.0003853259662299354</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0003117276292421399</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0003221612382256823</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.000319375367673671</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.0003387730124030231</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.0003356792886882121</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.0004995019014845697</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0004863446836503911</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.0005524964593692273</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.0006394120960769867</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0007305164436625136</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.0006062861891893107</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2495,7 +2531,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.319984243578351e-05</v>
+        <v>8.319984243578353e-05</v>
       </c>
       <c r="D36" t="n">
         <v>6.960833064139435e-05</v>
@@ -2513,7 +2549,7 @@
         <v>0.0001006043461325071</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0001349782572215017</v>
+        <v>0.0001349782572215018</v>
       </c>
       <c r="J36" t="n">
         <v>0.0001223729601393884</v>
@@ -2537,10 +2573,10 @@
         <v>0.0002421120970352584</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0002695542389557831</v>
+        <v>0.0002695542389557832</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0002924903648890849</v>
+        <v>0.0002924903648890848</v>
       </c>
       <c r="S36" t="n">
         <v>0.0003522816708381604</v>
@@ -2559,58 +2595,58 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01539884551618052</v>
+        <v>0.01538707992643224</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01266630650135971</v>
+        <v>0.01265525757917414</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01397598019977659</v>
+        <v>0.01396482207731104</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01284057009833811</v>
+        <v>0.01283040436750648</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01340449687768055</v>
+        <v>0.01339415528297337</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02159315950845399</v>
+        <v>0.02158549981338478</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02414076427466054</v>
+        <v>0.0241275366732903</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02144627491074662</v>
+        <v>0.0214352983711682</v>
       </c>
       <c r="K37" t="n">
-        <v>0.02181565807393582</v>
+        <v>0.02180346803218865</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02470451985912681</v>
+        <v>0.02469028489417943</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02399345542322011</v>
+        <v>0.02398009452247758</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0235815909564261</v>
+        <v>0.02356722618411068</v>
       </c>
       <c r="O37" t="n">
-        <v>0.03587422494115618</v>
+        <v>0.03585346868284228</v>
       </c>
       <c r="P37" t="n">
-        <v>0.03775817278507634</v>
+        <v>0.03773796725227189</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03247224921554848</v>
+        <v>0.03245406930963612</v>
       </c>
       <c r="R37" t="n">
-        <v>0.04005598237159314</v>
+        <v>0.04003472187476903</v>
       </c>
       <c r="S37" t="n">
-        <v>0.03624174694660657</v>
+        <v>0.03622142670059736</v>
       </c>
       <c r="T37" t="n">
-        <v>0.04225690900652355</v>
+        <v>0.04223249735737561</v>
       </c>
     </row>
     <row r="38">
@@ -2778,10 +2814,10 @@
         <v>0.0002823894265300068</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0002794347307699069</v>
+        <v>0.0002794347307699068</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0003883010189897506</v>
+        <v>0.0003883010189897505</v>
       </c>
       <c r="J43" t="n">
         <v>0.0003154865302452198</v>
@@ -2790,7 +2826,7 @@
         <v>0.0003520185963443392</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0003785629784290993</v>
+        <v>0.0003785629784290992</v>
       </c>
       <c r="M43" t="n">
         <v>0.0003613557640112981</v>
@@ -2799,19 +2835,19 @@
         <v>0.0004025256047155255</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0005367140204637204</v>
+        <v>0.0005367140204637203</v>
       </c>
       <c r="P43" t="n">
         <v>0.0005561727490918735</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0005107422209797427</v>
+        <v>0.0005107422209797428</v>
       </c>
       <c r="R43" t="n">
         <v>0.0006396417311605329</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0005834834830040191</v>
+        <v>0.000583483483004019</v>
       </c>
       <c r="T43" t="n">
         <v>0.0006458970782902846</v>
@@ -2827,58 +2863,58 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.000212266223679848</v>
+        <v>0.0004802415433402086</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001963485707158923</v>
+        <v>0.0004361710627541794</v>
       </c>
       <c r="E44" t="n">
-        <v>0.000189526257190104</v>
+        <v>0.0004682804727346709</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0001877033686441672</v>
+        <v>0.0004071850327870047</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0001970727688607449</v>
+        <v>0.0004343779971068692</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0001949743943223177</v>
+        <v>0.0005278835471159961</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0002943864972566735</v>
+        <v>0.000679712463486609</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0002530833147535648</v>
+        <v>0.0005648109439957046</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0002658627437143196</v>
+        <v>0.0005880239819400021</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0003355408189759192</v>
+        <v>0.0006549161866495903</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0003141145338186118</v>
+        <v>0.0006528875462216348</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0003256431706293014</v>
+        <v>0.0006613224593175136</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0005448387190046439</v>
+        <v>0.001044340620489214</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0005712171181306922</v>
+        <v>0.001057561801781083</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0005723263148515547</v>
+        <v>0.001124822774220782</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0006964200910004124</v>
+        <v>0.001335832187077399</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0007004332303655641</v>
+        <v>0.001430949674028078</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0007386710131225875</v>
+        <v>0.001344957202311898</v>
       </c>
     </row>
     <row r="45">
@@ -3011,7 +3047,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0006990888739242906</v>
+        <v>0.0006990888739242905</v>
       </c>
       <c r="D48" t="n">
         <v>0.0005838002011463132</v>
@@ -3041,10 +3077,10 @@
         <v>0.0004165846136062919</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0003903712838732112</v>
+        <v>0.0003903712838732111</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0003840346715677406</v>
+        <v>0.0003840346715677405</v>
       </c>
       <c r="O48" t="n">
         <v>0.0006015714738690202</v>
@@ -3251,7 +3287,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.04485939382801633</v>
+        <v>0.04485939382801634</v>
       </c>
       <c r="D54" t="n">
         <v>0.04079671677030716</v>
@@ -3266,16 +3302,16 @@
         <v>0.03177179894255752</v>
       </c>
       <c r="H54" t="n">
-        <v>0.04138105733444347</v>
+        <v>0.04138105733444346</v>
       </c>
       <c r="I54" t="n">
         <v>0.039929733207973</v>
       </c>
       <c r="J54" t="n">
-        <v>0.03273488823264455</v>
+        <v>0.03273488823264454</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0327052819206342</v>
+        <v>0.03270528192063419</v>
       </c>
       <c r="L54" t="n">
         <v>0.03378326389132339</v>
@@ -3287,13 +3323,13 @@
         <v>0.03485546014342787</v>
       </c>
       <c r="O54" t="n">
-        <v>0.08109589976990436</v>
+        <v>0.08109589976990438</v>
       </c>
       <c r="P54" t="n">
-        <v>0.07816104855333735</v>
+        <v>0.07816104855333736</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.08027754451085643</v>
+        <v>0.08027754451085642</v>
       </c>
       <c r="R54" t="n">
         <v>0.1248788369753337</v>
@@ -3302,7 +3338,7 @@
         <v>0.1300525997352245</v>
       </c>
       <c r="T54" t="n">
-        <v>0.1287698733765473</v>
+        <v>0.1287698733765472</v>
       </c>
     </row>
     <row r="55">
@@ -3318,7 +3354,7 @@
         <v>0.004032067601161434</v>
       </c>
       <c r="D55" t="n">
-        <v>0.003598279013072063</v>
+        <v>0.003598279013072062</v>
       </c>
       <c r="E55" t="n">
         <v>0.003456991785884843</v>
@@ -3327,16 +3363,16 @@
         <v>0.003997633048917358</v>
       </c>
       <c r="G55" t="n">
-        <v>0.004165520740067639</v>
+        <v>0.004165520740067638</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005148368519667294</v>
+        <v>0.005148368519667295</v>
       </c>
       <c r="I55" t="n">
         <v>0.006139426760218365</v>
       </c>
       <c r="J55" t="n">
-        <v>0.005396639914357363</v>
+        <v>0.005396639914357364</v>
       </c>
       <c r="K55" t="n">
         <v>0.005340776485904626</v>
@@ -3345,13 +3381,13 @@
         <v>0.005355358500876836</v>
       </c>
       <c r="M55" t="n">
-        <v>0.005553670025139319</v>
+        <v>0.00555367002513932</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005474506246428904</v>
+        <v>0.005474506246428903</v>
       </c>
       <c r="O55" t="n">
-        <v>0.007915310194993285</v>
+        <v>0.007915310194993284</v>
       </c>
       <c r="P55" t="n">
         <v>0.007818595540701672</v>
@@ -3360,7 +3396,7 @@
         <v>0.007827068348647137</v>
       </c>
       <c r="R55" t="n">
-        <v>0.009711025555168533</v>
+        <v>0.009711025555168527</v>
       </c>
       <c r="S55" t="n">
         <v>0.0101486454132752</v>
@@ -3385,7 +3421,7 @@
         <v>0.02043271272165454</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02134828075229537</v>
+        <v>0.02134828075229538</v>
       </c>
       <c r="F56" t="n">
         <v>0.02449929724794815</v>
@@ -3394,28 +3430,28 @@
         <v>0.02565785717090751</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02544226577252808</v>
+        <v>0.02544226577252809</v>
       </c>
       <c r="I56" t="n">
         <v>0.04167613363387705</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03525510063044047</v>
+        <v>0.03525510063044048</v>
       </c>
       <c r="K56" t="n">
-        <v>0.03779656474508723</v>
+        <v>0.03779656474508722</v>
       </c>
       <c r="L56" t="n">
-        <v>0.04563349212225863</v>
+        <v>0.04563349212225862</v>
       </c>
       <c r="M56" t="n">
-        <v>0.04362470149451168</v>
+        <v>0.04362470149451167</v>
       </c>
       <c r="N56" t="n">
         <v>0.04684216305278337</v>
       </c>
       <c r="O56" t="n">
-        <v>0.07141798964785304</v>
+        <v>0.07141798964785302</v>
       </c>
       <c r="P56" t="n">
         <v>0.06820778569237194</v>
@@ -3424,10 +3460,10 @@
         <v>0.06132715278761323</v>
       </c>
       <c r="R56" t="n">
-        <v>0.06833715538924046</v>
+        <v>0.06833715538924044</v>
       </c>
       <c r="S56" t="n">
-        <v>0.07758426094231721</v>
+        <v>0.07758426094231723</v>
       </c>
       <c r="T56" t="n">
         <v>0.08447865423187943</v>
@@ -3499,58 +3535,58 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3.679972869602325e-05</v>
+        <v>0.0002498822848703485</v>
       </c>
       <c r="D59" t="n">
         <v>3.206619694123202e-05</v>
       </c>
       <c r="E59" t="n">
-        <v>3.604334177373511e-05</v>
+        <v>0.0002498051294468902</v>
       </c>
       <c r="F59" t="n">
         <v>3.778809260674028e-05</v>
       </c>
       <c r="G59" t="n">
-        <v>3.343736668435694e-05</v>
+        <v>0.0002537829797373744</v>
       </c>
       <c r="H59" t="n">
-        <v>3.674720767851913e-05</v>
+        <v>0.0002087095914815304</v>
       </c>
       <c r="I59" t="n">
         <v>5.490594386080626e-05</v>
       </c>
       <c r="J59" t="n">
-        <v>4.920620319582618e-05</v>
+        <v>0.0002862583120207671</v>
       </c>
       <c r="K59" t="n">
         <v>4.385738925147525e-05</v>
       </c>
       <c r="L59" t="n">
-        <v>5.229633643287069e-05</v>
+        <v>0.0002604509874553475</v>
       </c>
       <c r="M59" t="n">
-        <v>6.480569766229182e-05</v>
+        <v>0.0002593540611892953</v>
       </c>
       <c r="N59" t="n">
-        <v>5.845481873305205e-05</v>
+        <v>0.0003333581110905998</v>
       </c>
       <c r="O59" t="n">
         <v>0.0001142422113033405</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0001469526142682561</v>
+        <v>0.000360006150112536</v>
       </c>
       <c r="Q59" t="n">
         <v>6.829379305853691e-05</v>
       </c>
       <c r="R59" t="n">
-        <v>0.000169139715000796</v>
+        <v>0.0004417662783191874</v>
       </c>
       <c r="S59" t="n">
         <v>0.0001578949049636056</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0001580128847149971</v>
+        <v>0.0005663086201013705</v>
       </c>
     </row>
     <row r="60">
@@ -3563,7 +3599,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.01446803630938622</v>
+        <v>0.01446803630938623</v>
       </c>
       <c r="D60" t="n">
         <v>0.01243860207818857</v>
@@ -3599,10 +3635,10 @@
         <v>0.02865610718500767</v>
       </c>
       <c r="O60" t="n">
-        <v>0.03924105655197339</v>
+        <v>0.0392410565519734</v>
       </c>
       <c r="P60" t="n">
-        <v>0.03822812227598787</v>
+        <v>0.03822812227598786</v>
       </c>
       <c r="Q60" t="n">
         <v>0.04089811355734511</v>
@@ -3611,7 +3647,7 @@
         <v>0.04904926313558835</v>
       </c>
       <c r="S60" t="n">
-        <v>0.04999672232880027</v>
+        <v>0.04999672232880025</v>
       </c>
       <c r="T60" t="n">
         <v>0.05226388157711057</v>
@@ -3627,58 +3663,58 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.667957613747765e-06</v>
+        <v>6.376965872790726e-06</v>
       </c>
       <c r="D61" t="n">
-        <v>1.870616835617006e-06</v>
+        <v>4.196634319827718e-06</v>
       </c>
       <c r="E61" t="n">
-        <v>1.718637343070267e-06</v>
+        <v>6.252879266473201e-06</v>
       </c>
       <c r="F61" t="n">
-        <v>1.601924044464208e-06</v>
+        <v>5.577382601451358e-06</v>
       </c>
       <c r="G61" t="n">
-        <v>1.750046892726258e-06</v>
+        <v>5.820327069665533e-06</v>
       </c>
       <c r="H61" t="n">
-        <v>1.232081471665732e-06</v>
+        <v>4.940539728839923e-06</v>
       </c>
       <c r="I61" t="n">
-        <v>1.713526597422531e-06</v>
+        <v>6.761373616002158e-06</v>
       </c>
       <c r="J61" t="n">
-        <v>1.410760616891009e-06</v>
+        <v>5.817612720516863e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>1.909262774227723e-06</v>
+        <v>3.803348947477757e-06</v>
       </c>
       <c r="L61" t="n">
-        <v>1.904000201377206e-06</v>
+        <v>7.071371494631438e-06</v>
       </c>
       <c r="M61" t="n">
-        <v>1.527359764456098e-06</v>
+        <v>6.357716736368691e-06</v>
       </c>
       <c r="N61" t="n">
-        <v>2.051267553046094e-06</v>
+        <v>7.774098267239613e-06</v>
       </c>
       <c r="O61" t="n">
-        <v>2.460553989491391e-06</v>
+        <v>4.891474611731651e-06</v>
       </c>
       <c r="P61" t="n">
-        <v>2.434986079614958e-06</v>
+        <v>9.935300788385182e-06</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.027354418868953e-06</v>
+        <v>9.113687903084382e-06</v>
       </c>
       <c r="R61" t="n">
-        <v>2.633903424570365e-06</v>
+        <v>1.087422055413614e-05</v>
       </c>
       <c r="S61" t="n">
-        <v>2.69537605142878e-06</v>
+        <v>8.902392521551031e-06</v>
       </c>
       <c r="T61" t="n">
-        <v>2.757908436614163e-06</v>
+        <v>1.055863216416586e-05</v>
       </c>
     </row>
     <row r="62">
@@ -3690,24 +3726,60 @@
           <t>vacuole-isolation membrane contact site</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>0.0002130825561743253</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0002137617876731552</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0002203456130530174</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.0001719623838030113</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.0002370521088249409</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.0002081546510224769</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.0001945483635270035</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.0002749032923575477</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.00021305353584428</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.0002726265633183914</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.0004082957353863733</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -3728,7 +3800,7 @@
         <v>0.01082985385671924</v>
       </c>
       <c r="F63" t="n">
-        <v>0.008724222536167224</v>
+        <v>0.008724222536167225</v>
       </c>
       <c r="G63" t="n">
         <v>0.01057392880511603</v>
@@ -3764,7 +3836,7 @@
         <v>0.01210777587974611</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01746091258550525</v>
+        <v>0.01746091258550524</v>
       </c>
       <c r="S63" t="n">
         <v>0.01815521330080052</v>
@@ -3853,7 +3925,7 @@
         <v>0.03762958385703769</v>
       </c>
       <c r="E65" t="n">
-        <v>0.03754142239295561</v>
+        <v>0.03754142239295562</v>
       </c>
       <c r="F65" t="n">
         <v>0.0190360355058308</v>
@@ -3862,7 +3934,7 @@
         <v>0.02073676482215338</v>
       </c>
       <c r="H65" t="n">
-        <v>0.03314073161028488</v>
+        <v>0.03314073161028487</v>
       </c>
       <c r="I65" t="n">
         <v>0.03084855677968054</v>
@@ -3871,19 +3943,19 @@
         <v>0.02661722477301867</v>
       </c>
       <c r="K65" t="n">
-        <v>0.02799691420968129</v>
+        <v>0.0279969142096813</v>
       </c>
       <c r="L65" t="n">
         <v>0.03281186945799891</v>
       </c>
       <c r="M65" t="n">
-        <v>0.03117465532044575</v>
+        <v>0.03117465532044574</v>
       </c>
       <c r="N65" t="n">
         <v>0.03247092442224846</v>
       </c>
       <c r="O65" t="n">
-        <v>0.05200955397207813</v>
+        <v>0.05200955397207815</v>
       </c>
       <c r="P65" t="n">
         <v>0.05461891718174219</v>
@@ -3895,10 +3967,10 @@
         <v>0.0571132133385217</v>
       </c>
       <c r="S65" t="n">
-        <v>0.05172275960625485</v>
+        <v>0.05172275960625486</v>
       </c>
       <c r="T65" t="n">
-        <v>0.05861669645682304</v>
+        <v>0.05861669645682305</v>
       </c>
     </row>
     <row r="66">
@@ -3923,10 +3995,10 @@
         <v>8.937695677627795e-05</v>
       </c>
       <c r="G66" t="n">
-        <v>9.938767877273358e-05</v>
+        <v>9.938767877273357e-05</v>
       </c>
       <c r="H66" t="n">
-        <v>6.711668808356003e-05</v>
+        <v>6.711668808356005e-05</v>
       </c>
       <c r="I66" t="n">
         <v>0.0001246067020743092</v>
@@ -3944,7 +4016,7 @@
         <v>0.0001333340957802041</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0001326910703642349</v>
+        <v>0.0001326910703642348</v>
       </c>
       <c r="O66" t="n">
         <v>0.0001945943233004497</v>
@@ -4150,7 +4222,7 @@
         <v>0.02125358317864736</v>
       </c>
       <c r="L71" t="n">
-        <v>0.02291078666488329</v>
+        <v>0.0229107866648833</v>
       </c>
       <c r="M71" t="n">
         <v>0.02198522410005313</v>
@@ -4162,10 +4234,10 @@
         <v>0.03207431043001457</v>
       </c>
       <c r="P71" t="n">
-        <v>0.030960404909403</v>
+        <v>0.03096040490940301</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.03394215683414924</v>
+        <v>0.03394215683414923</v>
       </c>
       <c r="R71" t="n">
         <v>0.04124834030465082</v>
@@ -4174,7 +4246,7 @@
         <v>0.04104432782998569</v>
       </c>
       <c r="T71" t="n">
-        <v>0.04335283458137786</v>
+        <v>0.04335283458137785</v>
       </c>
     </row>
     <row r="72">
@@ -4187,7 +4259,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.00575969374150541</v>
+        <v>0.005759693741505409</v>
       </c>
       <c r="D72" t="n">
         <v>0.005332391483509461</v>
@@ -4202,10 +4274,10 @@
         <v>0.00485284813267673</v>
       </c>
       <c r="H72" t="n">
-        <v>0.005312106374712381</v>
+        <v>0.00531210637471238</v>
       </c>
       <c r="I72" t="n">
-        <v>0.007777404363626632</v>
+        <v>0.007777404363626631</v>
       </c>
       <c r="J72" t="n">
         <v>0.006391979559556425</v>
@@ -4214,10 +4286,10 @@
         <v>0.006925538516561166</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0084521679162676</v>
+        <v>0.008452167916267602</v>
       </c>
       <c r="M72" t="n">
-        <v>0.007669433634405826</v>
+        <v>0.007669433634405827</v>
       </c>
       <c r="N72" t="n">
         <v>0.007590387820219657</v>
@@ -4251,58 +4323,58 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.002355093467949171</v>
+        <v>0.002623068787609532</v>
       </c>
       <c r="D73" t="n">
-        <v>0.002169772338625545</v>
+        <v>0.002409594830663832</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0021679167542479</v>
+        <v>0.002446670969792467</v>
       </c>
       <c r="F73" t="n">
-        <v>0.002019605690753019</v>
+        <v>0.002239087354895857</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002089832187708588</v>
+        <v>0.002327137415954712</v>
       </c>
       <c r="H73" t="n">
-        <v>0.002967661880122938</v>
+        <v>0.003300571032916616</v>
       </c>
       <c r="I73" t="n">
-        <v>0.003424940392448706</v>
+        <v>0.003810266358678641</v>
       </c>
       <c r="J73" t="n">
-        <v>0.00276245237337887</v>
+        <v>0.003074180002621009</v>
       </c>
       <c r="K73" t="n">
-        <v>0.003020162206052732</v>
+        <v>0.003342323444278414</v>
       </c>
       <c r="L73" t="n">
-        <v>0.003574139150587961</v>
+        <v>0.003893514518261631</v>
       </c>
       <c r="M73" t="n">
-        <v>0.00340831313370631</v>
+        <v>0.003747086146109333</v>
       </c>
       <c r="N73" t="n">
-        <v>0.003320550505396871</v>
+        <v>0.003656229794085084</v>
       </c>
       <c r="O73" t="n">
-        <v>0.004871506523240686</v>
+        <v>0.005371008424725256</v>
       </c>
       <c r="P73" t="n">
-        <v>0.005363508048925578</v>
+        <v>0.00584985273257597</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.004632169136017064</v>
+        <v>0.005184665595386291</v>
       </c>
       <c r="R73" t="n">
-        <v>0.00558122959611235</v>
+        <v>0.006220641692189337</v>
       </c>
       <c r="S73" t="n">
-        <v>0.005492268511436135</v>
+        <v>0.00622278495509865</v>
       </c>
       <c r="T73" t="n">
-        <v>0.005923664858647529</v>
+        <v>0.00652995104783684</v>
       </c>
     </row>
     <row r="74">
@@ -4342,7 +4414,7 @@
         <v>0.0004299942178182261</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0005601051045557651</v>
+        <v>0.000560105104555765</v>
       </c>
       <c r="M74" t="n">
         <v>0.0005738013630020112</v>
@@ -4646,24 +4718,60 @@
           <t>mitochondrial ribosome</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>1.343618885026561e-05</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1.093839033090519e-05</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.410648129005907e-05</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.307518705194942e-05</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.29417667462104e-05</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.831194421034347e-05</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2.730599709530708e-05</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.215951290251428e-05</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2.282147753637877e-05</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2.212507968524945e-05</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.600454568600401e-05</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2.468505971188576e-05</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4.359010840019566e-05</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4.664340663883969e-05</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4.191921403101061e-05</v>
+      </c>
+      <c r="R82" t="n">
+        <v>4.64349630262406e-05</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5.801490806636295e-05</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5.473777838294026e-05</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -4714,7 +4822,7 @@
         <v>0.02108879396683409</v>
       </c>
       <c r="P83" t="n">
-        <v>0.02270046034455987</v>
+        <v>0.02270046034455986</v>
       </c>
       <c r="Q83" t="n">
         <v>0.0190386351649628</v>
@@ -4726,7 +4834,7 @@
         <v>0.02560952748971333</v>
       </c>
       <c r="T83" t="n">
-        <v>0.02586862924910177</v>
+        <v>0.02586862924910176</v>
       </c>
     </row>
     <row r="84">
@@ -5455,58 +5563,58 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.92475425590595e-05</v>
+        <v>7.481952810779589e-06</v>
       </c>
       <c r="D98" t="n">
-        <v>1.798929183593718e-05</v>
+        <v>6.940369650377272e-06</v>
       </c>
       <c r="E98" t="n">
-        <v>1.84391786751878e-05</v>
+        <v>7.28105620963265e-06</v>
       </c>
       <c r="F98" t="n">
-        <v>1.647090186034798e-05</v>
+        <v>6.305171028715206e-06</v>
       </c>
       <c r="G98" t="n">
-        <v>1.69235122419178e-05</v>
+        <v>6.581917534734202e-06</v>
       </c>
       <c r="H98" t="n">
-        <v>1.443901336223039e-05</v>
+        <v>6.779318293021781e-06</v>
       </c>
       <c r="I98" t="n">
-        <v>2.310557426785938e-05</v>
+        <v>9.877972897613622e-06</v>
       </c>
       <c r="J98" t="n">
-        <v>1.954085713513446e-05</v>
+        <v>8.564317556713314e-06</v>
       </c>
       <c r="K98" t="n">
-        <v>2.084939795826668e-05</v>
+        <v>8.659356211097304e-06</v>
       </c>
       <c r="L98" t="n">
-        <v>2.611691549572809e-05</v>
+        <v>1.188195054834323e-05</v>
       </c>
       <c r="M98" t="n">
-        <v>2.51165679383747e-05</v>
+        <v>1.175566719584849e-05</v>
       </c>
       <c r="N98" t="n">
-        <v>2.592591418635723e-05</v>
+        <v>1.156114187092594e-05</v>
       </c>
       <c r="O98" t="n">
-        <v>4.036953929876455e-05</v>
+        <v>1.961328098486516e-05</v>
       </c>
       <c r="P98" t="n">
-        <v>4.027094922799938e-05</v>
+        <v>2.006541642355189e-05</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.847478381261837e-05</v>
+        <v>2.0294877900255e-05</v>
       </c>
       <c r="R98" t="n">
-        <v>4.155733199215433e-05</v>
+        <v>2.02968351680744e-05</v>
       </c>
       <c r="S98" t="n">
-        <v>4.455878182148784e-05</v>
+        <v>2.423853581228802e-05</v>
       </c>
       <c r="T98" t="n">
-        <v>5.100504696947197e-05</v>
+        <v>2.659339782151472e-05</v>
       </c>
     </row>
     <row r="99">
@@ -5694,24 +5802,60 @@
           <t>vacuolar membrane</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>2.98335338428911e-06</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.326017484210712e-06</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.327918442397001e-06</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.044294698317283e-06</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.202507524606706e-06</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.272161433201636e-06</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2.418841196447755e-06</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.315487074634901e-06</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1.894086173250034e-06</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2.035526734757794e-06</v>
+      </c>
+      <c r="M104" t="n">
+        <v>2.278659091816748e-06</v>
+      </c>
+      <c r="N104" t="n">
+        <v>2.664565033099413e-06</v>
+      </c>
+      <c r="O104" t="n">
+        <v>2.43092062224026e-06</v>
+      </c>
+      <c r="P104" t="n">
+        <v>3.399952774540204e-06</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>2.180373415741979e-06</v>
+      </c>
+      <c r="R104" t="n">
+        <v>4.1319991553471e-06</v>
+      </c>
+      <c r="S104" t="n">
+        <v>2.295267004186855e-06</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3.358064969007899e-06</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -5932,13 +6076,13 @@
         <v>0.0006478014013573462</v>
       </c>
       <c r="N110" t="n">
-        <v>0.000670611704854507</v>
+        <v>0.0006706117048545069</v>
       </c>
       <c r="O110" t="n">
-        <v>0.001055216403329197</v>
+        <v>0.001055216403329198</v>
       </c>
       <c r="P110" t="n">
-        <v>0.001161792543355036</v>
+        <v>0.001161792543355035</v>
       </c>
       <c r="Q110" t="n">
         <v>0.0008645508298559274</v>
@@ -6786,24 +6930,60 @@
           <t>phagophore</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>1.725654874753851e-06</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.206323481005933e-06</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.931163858669867e-06</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.867772652332568e-06</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1.436296823972556e-06</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2.629005822131873e-06</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.091365028990953e-06</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>3.131844558496438e-06</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2.551697880095845e-06</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3.058265681094106e-06</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>4.100361934230021e-06</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>3.905960068473448e-06</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4.108317974218673e-06</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3.911749465935397e-06</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4.442658758543797e-06</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
